--- a/p6_deployment/data/england/missing/data_understanding/df_match_miss.xlsx
+++ b/p6_deployment/data/england/missing/data_understanding/df_match_miss.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV41" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -17132,7 +17132,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -18522,7 +18522,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>6HLBNw1</t>
+          <t>6HLBNw1o</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -19078,7 +19078,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
@@ -20460,7 +20460,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -21846,7 +21846,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
@@ -22412,7 +22412,7 @@
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
@@ -23236,7 +23236,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -23246,7 +23246,7 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
@@ -23792,7 +23792,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -24636,7 +24636,7 @@
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -25182,7 +25182,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -25470,7 +25470,7 @@
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
@@ -25738,7 +25738,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
@@ -25748,7 +25748,7 @@
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -26012,7 +26012,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
@@ -26300,7 +26300,7 @@
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
@@ -26854,7 +26854,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
@@ -27132,7 +27132,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
@@ -28252,7 +28252,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
@@ -28262,7 +28262,7 @@
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -28540,7 +28540,7 @@
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -29104,7 +29104,7 @@
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
@@ -29372,7 +29372,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
@@ -29650,7 +29650,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -29660,7 +29660,7 @@
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
@@ -29928,7 +29928,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
@@ -30206,7 +30206,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -30216,7 +30216,7 @@
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
@@ -30480,7 +30480,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -30490,7 +30490,7 @@
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
@@ -30766,7 +30766,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -31054,7 +31054,7 @@
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
@@ -31322,7 +31322,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
@@ -31332,7 +31332,7 @@
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
@@ -31610,7 +31610,7 @@
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
@@ -31888,7 +31888,7 @@
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
@@ -32156,7 +32156,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>EoQjC3V</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -32166,7 +32166,7 @@
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>lAbHYaQ</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
@@ -32434,7 +32434,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -32444,7 +32444,7 @@
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
@@ -32712,7 +32712,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>K6A2elS</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -32722,7 +32722,7 @@
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>xpALVpw</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
@@ -32990,7 +32990,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>MBpIn2M</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>8QQVnKh</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>va62Pxq</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -33278,7 +33278,7 @@
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>vBIoDoo</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
@@ -33556,7 +33556,7 @@
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>hUGEt9y</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>GxXzVQF</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -33834,7 +33834,7 @@
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>pYizckp</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
@@ -34102,7 +34102,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -34112,7 +34112,7 @@
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
@@ -34380,7 +34380,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>IoJ2QpO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -34390,7 +34390,7 @@
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
@@ -34658,7 +34658,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>0K79iBX</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -34668,7 +34668,7 @@
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>CznGurC</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
@@ -35248,7 +35248,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
@@ -35559,7 +35559,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -35569,7 +35569,7 @@
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
@@ -35870,7 +35870,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>dpjHQ7z</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -35880,7 +35880,7 @@
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>x6CvOHH</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
@@ -36189,7 +36189,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>zuJM7XD</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
@@ -36199,7 +36199,7 @@
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
@@ -36508,7 +36508,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>hxNijWr</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -36518,7 +36518,7 @@
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>hbOpz9h</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>4rSZHs2</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -36829,7 +36829,7 @@
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
@@ -37098,7 +37098,7 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
@@ -37353,7 +37353,7 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -37363,7 +37363,7 @@
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
@@ -37608,7 +37608,7 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
@@ -37618,7 +37618,7 @@
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
@@ -37862,7 +37862,7 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -37872,7 +37872,7 @@
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
@@ -38116,7 +38116,7 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -38126,7 +38126,7 @@
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
@@ -38370,7 +38370,7 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
@@ -38624,7 +38624,7 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -38634,7 +38634,7 @@
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
@@ -38878,7 +38878,7 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -38888,7 +38888,7 @@
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
@@ -39132,7 +39132,7 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -39142,7 +39142,7 @@
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
@@ -39386,7 +39386,7 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -39396,7 +39396,7 @@
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
@@ -39640,7 +39640,7 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
@@ -39886,7 +39886,7 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -39896,7 +39896,7 @@
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
@@ -40140,7 +40140,7 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>zNcAe8S</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
@@ -40150,7 +40150,7 @@
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
@@ -40386,7 +40386,7 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -40396,7 +40396,7 @@
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
@@ -40640,7 +40640,7 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
@@ -40894,7 +40894,7 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
@@ -41156,7 +41156,7 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
@@ -41413,7 +41413,7 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
@@ -41667,7 +41667,7 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
@@ -41677,7 +41677,7 @@
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
@@ -41921,7 +41921,7 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
@@ -42175,7 +42175,7 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -42185,7 +42185,7 @@
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
@@ -42437,7 +42437,7 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -42447,7 +42447,7 @@
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>zNcAe8S</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
@@ -42683,7 +42683,7 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -42693,7 +42693,7 @@
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
@@ -42937,7 +42937,7 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -42947,7 +42947,7 @@
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
@@ -43183,7 +43183,7 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
@@ -43193,7 +43193,7 @@
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
@@ -43437,7 +43437,7 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
@@ -43691,7 +43691,7 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -43701,7 +43701,7 @@
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
@@ -43945,7 +43945,7 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -43955,7 +43955,7 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
@@ -44199,7 +44199,7 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -44209,7 +44209,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -44453,7 +44453,7 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -44463,7 +44463,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -44707,7 +44707,7 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -44961,7 +44961,7 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -44971,7 +44971,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -45215,7 +45215,7 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
@@ -45225,7 +45225,7 @@
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
@@ -45469,7 +45469,7 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
@@ -45479,7 +45479,7 @@
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
@@ -45723,7 +45723,7 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
@@ -45733,7 +45733,7 @@
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
@@ -45977,7 +45977,7 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -45987,7 +45987,7 @@
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
@@ -46231,7 +46231,7 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -46241,7 +46241,7 @@
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
@@ -46485,7 +46485,7 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -46495,7 +46495,7 @@
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
@@ -46739,7 +46739,7 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>zNcAe8S</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
@@ -46993,7 +46993,7 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
@@ -47003,7 +47003,7 @@
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
@@ -47247,7 +47247,7 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
@@ -47257,7 +47257,7 @@
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
@@ -47501,7 +47501,7 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
@@ -47511,7 +47511,7 @@
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
@@ -47755,7 +47755,7 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -47765,7 +47765,7 @@
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
@@ -48009,7 +48009,7 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -48019,7 +48019,7 @@
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
@@ -48263,7 +48263,7 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -48273,7 +48273,7 @@
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
@@ -48517,7 +48517,7 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -48527,7 +48527,7 @@
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
@@ -48771,7 +48771,7 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -48781,7 +48781,7 @@
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
@@ -49025,7 +49025,7 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
@@ -49035,7 +49035,7 @@
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
@@ -49279,7 +49279,7 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
@@ -49289,7 +49289,7 @@
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
@@ -49533,7 +49533,7 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -49543,7 +49543,7 @@
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
@@ -49787,7 +49787,7 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -49797,7 +49797,7 @@
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
@@ -50041,7 +50041,7 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -50051,7 +50051,7 @@
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
@@ -50295,7 +50295,7 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -50305,7 +50305,7 @@
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
@@ -50549,7 +50549,7 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -50559,7 +50559,7 @@
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
@@ -50811,7 +50811,7 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
@@ -50821,7 +50821,7 @@
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
@@ -51065,7 +51065,7 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
@@ -51075,7 +51075,7 @@
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
@@ -51319,7 +51319,7 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
@@ -51329,7 +51329,7 @@
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
@@ -51573,7 +51573,7 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -51583,7 +51583,7 @@
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
@@ -51827,7 +51827,7 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -51837,7 +51837,7 @@
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
@@ -52081,7 +52081,7 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -52091,7 +52091,7 @@
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
@@ -52335,7 +52335,7 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -52345,7 +52345,7 @@
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
@@ -52589,7 +52589,7 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
@@ -52599,7 +52599,7 @@
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
@@ -52843,7 +52843,7 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
@@ -52853,7 +52853,7 @@
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
@@ -53097,7 +53097,7 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
@@ -53107,7 +53107,7 @@
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
@@ -53351,7 +53351,7 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -53361,7 +53361,7 @@
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
@@ -53605,7 +53605,7 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -53615,7 +53615,7 @@
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
@@ -53859,7 +53859,7 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -53869,7 +53869,7 @@
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
@@ -54113,7 +54113,7 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -54123,7 +54123,7 @@
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
@@ -54367,7 +54367,7 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -54377,7 +54377,7 @@
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
@@ -54621,7 +54621,7 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -54631,7 +54631,7 @@
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
@@ -54875,7 +54875,7 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
@@ -54885,7 +54885,7 @@
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
@@ -55129,7 +55129,7 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -55139,7 +55139,7 @@
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
@@ -55383,7 +55383,7 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -55393,7 +55393,7 @@
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
@@ -55637,7 +55637,7 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -55647,7 +55647,7 @@
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
@@ -55891,7 +55891,7 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
@@ -56145,7 +56145,7 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -56155,7 +56155,7 @@
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
@@ -56399,7 +56399,7 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -56409,7 +56409,7 @@
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
@@ -56653,7 +56653,7 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
@@ -56663,7 +56663,7 @@
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
@@ -56907,7 +56907,7 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -56917,7 +56917,7 @@
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
@@ -57153,7 +57153,7 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -57163,7 +57163,7 @@
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>8tPSZqt</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
@@ -57407,7 +57407,7 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -57417,7 +57417,7 @@
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
@@ -57661,7 +57661,7 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -57671,7 +57671,7 @@
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
@@ -57923,7 +57923,7 @@
       <c r="AT213" t="inlineStr"/>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -57933,7 +57933,7 @@
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
@@ -58177,7 +58177,7 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
@@ -58187,7 +58187,7 @@
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
@@ -58431,7 +58431,7 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
@@ -58685,7 +58685,7 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>nglXJS0</t>
+          <t>nglXJS0e</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
@@ -58695,7 +58695,7 @@
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
@@ -58947,7 +58947,7 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -58957,7 +58957,7 @@
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
@@ -59201,7 +59201,7 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -59211,7 +59211,7 @@
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
@@ -59447,7 +59447,7 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -59457,7 +59457,7 @@
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
@@ -59693,7 +59693,7 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -59703,7 +59703,7 @@
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
@@ -59947,7 +59947,7 @@
       <c r="AT221" t="inlineStr"/>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -59957,7 +59957,7 @@
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
@@ -60201,7 +60201,7 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -60211,7 +60211,7 @@
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
@@ -60447,7 +60447,7 @@
       <c r="AT223" t="inlineStr"/>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
@@ -60457,7 +60457,7 @@
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
@@ -60701,7 +60701,7 @@
       <c r="AT224" t="inlineStr"/>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -60711,7 +60711,7 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
@@ -60963,7 +60963,7 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -60973,7 +60973,7 @@
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
@@ -61217,7 +61217,7 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -61227,7 +61227,7 @@
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>lYgfxNV</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
@@ -61471,7 +61471,7 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>4fMAHvL</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -61481,7 +61481,7 @@
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
@@ -61725,7 +61725,7 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -61735,7 +61735,7 @@
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>nglXJS0</t>
+          <t>nglXJS0e</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
@@ -61979,7 +61979,7 @@
       <c r="AT229" t="inlineStr"/>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
@@ -61989,7 +61989,7 @@
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
@@ -62233,7 +62233,7 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
@@ -62243,7 +62243,7 @@
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>neBDmKp</t>
+          <t>neBDmKpm</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
@@ -62495,7 +62495,7 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
@@ -62505,7 +62505,7 @@
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
@@ -62749,7 +62749,7 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Aotm1TV</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -62759,7 +62759,7 @@
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
@@ -63003,7 +63003,7 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -63013,7 +63013,7 @@
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
@@ -63257,7 +63257,7 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -63267,7 +63267,7 @@
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>nJsvYDR</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
@@ -63511,7 +63511,7 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>AHNtWa3</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -63521,7 +63521,7 @@
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>MsDWbjn</t>
+          <t>MsDWbjnD</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
@@ -63765,7 +63765,7 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>joMpXpx</t>
+          <t>joMpXpxG</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
@@ -63775,7 +63775,7 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>n94TZqs</t>
+          <t>n94TZqsm</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
@@ -64019,7 +64019,7 @@
       <c r="AT237" t="inlineStr"/>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>pdaUMZY</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
@@ -64029,7 +64029,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Y39YvFx</t>
+          <t>Y39YvFx6</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -64281,7 +64281,7 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>phM8NEl</t>
+          <t>phM8NElP</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
@@ -64291,7 +64291,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>fcpIzd9</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -64535,7 +64535,7 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>nglXJS0</t>
+          <t>nglXJS0e</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -64545,7 +64545,7 @@
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>6wEAqBA</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
@@ -64789,7 +64789,7 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>GKEUt35</t>
+          <t>GKEUt35A</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -64799,7 +64799,7 @@
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>lhUKMQZ</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
@@ -65051,7 +65051,7 @@
       <c r="AT241" t="inlineStr"/>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>C2sV0kf</t>
+          <t>C2sV0kf7</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -65061,7 +65061,7 @@
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>OS3AwgC</t>
+          <t>OS3AwgCU</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
@@ -65305,7 +65305,7 @@
       <c r="AT242" t="inlineStr"/>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>bPZzRCh</t>
+          <t>bPZzRChI</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -65315,7 +65315,7 @@
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>U3POrPv</t>
+          <t>U3POrPvM</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
@@ -65559,7 +65559,7 @@
       <c r="AT243" t="inlineStr"/>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>nPjMw0n</t>
+          <t>nPjMw0nA</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
@@ -65569,7 +65569,7 @@
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>UwJevjp</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
@@ -65813,7 +65813,7 @@
       <c r="AT244" t="inlineStr"/>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>tMUvLt7</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
@@ -65823,7 +65823,7 @@
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>OEy2L7Z</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
